--- a/ra/time data (version 2).xlsb.xlsx
+++ b/ra/time data (version 2).xlsb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\uni\masters nu\RA\pythonCode\ra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1914B741-B596-4923-A2A9-D9E45DFB1586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F5C170-E130-4337-9EBC-B65CD725487F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3645" windowWidth="21600" windowHeight="11835" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="100s" sheetId="1" r:id="rId1"/>
@@ -1697,7 +1697,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Log Time vs N</a:t>
             </a:r>
           </a:p>
@@ -1897,7 +1897,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-139D-4D6D-9FD7-1D49CA7535CA}"/>
+              <c16:uniqueId val="{00000000-C9A2-473C-89D9-4A600C4BCEC5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2059,7 +2059,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-139D-4D6D-9FD7-1D49CA7535CA}"/>
+              <c16:uniqueId val="{00000001-C9A2-473C-89D9-4A600C4BCEC5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2221,7 +2221,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-139D-4D6D-9FD7-1D49CA7535CA}"/>
+              <c16:uniqueId val="{00000002-C9A2-473C-89D9-4A600C4BCEC5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2245,6 +2245,66 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2267,7 +2327,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2300,16 +2360,68 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2326,7 +2438,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2348,7 +2460,9 @@
       <c:spPr>
         <a:noFill/>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -2361,15 +2475,19 @@
           <c:yMode val="edge"/>
           <c:x val="0.13053999828968746"/>
           <c:y val="0.11762405856546715"/>
-          <c:w val="5.1805962573744771E-2"/>
-          <c:h val="0.12652380977682376"/>
+          <c:w val="0.10201027786493486"/>
+          <c:h val="0.1965019209542527"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -2378,7 +2496,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3020,6 +3138,66 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3082,6 +3260,4533 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732662447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13053999828968746"/>
+          <c:y val="0.11762405856546715"/>
+          <c:w val="0.10201027786493486"/>
+          <c:h val="0.1965019209542527"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Time vs N</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NE time</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'10s 1000'!$B$2:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.5242</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76559999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0414000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3345</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5966</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.8852</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.2153</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5362</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.8161999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.1326000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5352000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.8248000000000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.2390999999999996</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.5629999999999997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.8201999999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.2755000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.6651999999999996</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.0277000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.3319999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3223-4F17-B2B3-FFF3D9CF7F8F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LE time</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'10s 1000'!$C$2:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.1196999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.6886999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.832800000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33.666400000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72.194699999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>151.7961</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>292.39670000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>482.36649999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>700.24310000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1275.1572000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1740.0181</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2551.3613</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3370.7561000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4842.2988999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8427.7610959999693</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>11210.669748299901</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14625.7355764</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>16407.207656699899</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>17768.265146199901</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3223-4F17-B2B3-FFF3D9CF7F8F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ftst time</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'10s 1000'!$D$2:$D$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.17069999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25580000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.34739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.41699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.50370000000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58930000000000005</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.72140000000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.78300000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.85570000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96150000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0361</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1577999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2376</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2986</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4140999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5068999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.5782</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6807000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.7574000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3223-4F17-B2B3-FFF3D9CF7F8F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="732662447"/>
+        <c:axId val="732663887"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="732662447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732663887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="732663887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Time, s</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732662447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13053999828968746"/>
+          <c:y val="0.11762405856546715"/>
+          <c:w val="8.5575236558302514E-2"/>
+          <c:h val="0.15372848925798605"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Log Time vs N</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log NE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'20s 2000'!$E$2:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.17912072960929923</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.26688993247105292</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.40859607646278268</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53064785352748556</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.77826704680664749</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.84486221613752133</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.91882162594644479</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.96270546410180979</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.0239640369866647</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.0678330862343137</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1250190736565042</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2045784641095207</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2068987019193613</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2361844428801496</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.259271263185658</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.3012145316076791</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3255505532952461</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.3520956505279338</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3096110069525659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-74DD-4CF3-8994-6CA467525292}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log LE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'20s 2000'!$F$2:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.36068075590673898</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98361730349472876</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4609198138946675</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8612580333896194</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1768526827455936</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.464359288292099</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.7060008232242336</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.9274268362844258</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.1256414735043663</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.3018647321002264</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.4711752869273647</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.6268820043517778</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.7693818979616709</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.9046200224387309</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.0334210290741446</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.1832130896040161</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.2754123710177439</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.4002371006387984</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.5676086152707969</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-74DD-4CF3-8994-6CA467525292}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log Ftst</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'20s 2000'!$G$2:$G$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>-0.38806437495987745</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.2277516600281464</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.6981316252039753E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-9.7499670721832143E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.30272044989613406</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.31756193662124627</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.39455673936365637</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.44543294229516656</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.51324424308392258</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56206673449545508</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.59713550679772964</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.62979682525550629</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.67520073089069388</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.70417626476122619</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.72892975334370924</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.74462933325109992</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.774786947269548</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.79123436512436673</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.82463991130814507</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-74DD-4CF3-8994-6CA467525292}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="732662447"/>
+        <c:axId val="732663887"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="732662447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732663887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="732663887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732662447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13053999828968746"/>
+          <c:y val="0.11762405856546715"/>
+          <c:w val="0.10201027786493486"/>
+          <c:h val="0.1965019209542527"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Log Time vs N</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log NE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'30s 3000'!$E$2:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.25095643933189343</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42535485766551501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69589301068015452</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.83372705928606883</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.94060114418270613</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0398581020361306</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0876359189806979</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1570576504069054</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2016237723514125</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2526200507882073</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.3202854873899716</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2983355430826178</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1858395150042349</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1887457324264934</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2170863169884278</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.248916892312752</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.2787513151863827</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.3023330936564801</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3336608424638372</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1E02-408F-895C-4C842BA6D16F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log LE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'30s 3000'!$F$2:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.51433350099549968</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1482121787450121</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6272577529787677</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0114154337011714</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.3318139782597158</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6202452317349185</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.958009235804588</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.167329253811439</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.3719726736643723</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.5117680538642713</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.6886444867050172</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.9057017652787542</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.9677113046188439</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.0880132115585583</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.2159898031088741</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.342868780383359</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.4681859662259837</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.6438190644616952</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.7412217912465104</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1E02-408F-895C-4C842BA6D16F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log Ftst</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'30s 3000'!$G$2:$G$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>-0.25602013475815716</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.5024091587952087E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.1513805095089159E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33713966272456086</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.43068766897666905</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.50502781581696332</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.60313354219880733</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.64391633436409879</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.67862762177290059</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.73001472091972386</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.774108025508218</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6297153326471322</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.83626713455867729</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.66116880924155608</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.67699522524215427</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.70485374456628858</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.73194314666858362</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.74462933325109992</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.77613434316584407</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1E02-408F-895C-4C842BA6D16F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="732662447"/>
+        <c:axId val="732663887"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="732662447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732663887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="732663887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732662447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13053999828968746"/>
+          <c:y val="0.11762405856546715"/>
+          <c:w val="0.10201027786493486"/>
+          <c:h val="0.1965019209542527"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Log Time vs N</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log NE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'40s 4000'!$E$2:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.37383114507383042</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.57769855750925869</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6902492556890788</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.79971264242099849</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.87879745052912372</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.95206559018505033</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0161304050797639</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0698123445446543</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1334558735465661</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.4184222801796331</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.3391691078314798</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2542410381636646</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2870018022964353</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3231571845930392</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.3576204411621846</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.3821737927893971</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.4125075864510788</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.4395695171471754</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.4634808853560093</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1002-4728-856D-CF4AC5ED2FCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log LE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'40s 4000'!$F$2:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.71443319838513852</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3382644710825842</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8244134187280845</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2210495831309771</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5477012993570387</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.832572898793499</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.0777538008309633</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.2423443638663829</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4318787840667619</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.755981536128548</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.9300885869662117</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.0414433142515032</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.1408236655760318</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.2119098217974935</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.3563986364523366</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.4932838820112169</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.5899965896699015</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.758048832228817</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.8399777690945296</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1002-4728-856D-CF4AC5ED2FCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log Ftst</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'40s 4000'!$G$2:$G$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>-0.10623823794205658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15341848503771086</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21258707812389371</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29887489970469894</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.37817979038095018</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.47092475329996797</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.50956540322279242</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.55837252216915689</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.60689705226627222</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.77782540731578609</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.87394804398844594</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.74411296792625192</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.74741180788642325</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.77542110822219423</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.80924987473863941</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.83145382933658074</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.86286452691444582</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.87808498356654152</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.91170080309601198</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1002-4728-856D-CF4AC5ED2FCE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="732662447"/>
+        <c:axId val="732663887"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="732662447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732663887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="732663887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732662447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13053999828968746"/>
+          <c:y val="0.11762405856546715"/>
+          <c:w val="0.10201027786493486"/>
+          <c:h val="0.1965019209542527"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>Log Time vs N</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log NE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'50s 5000'!$E$2:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.46899680905960173</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.82456836736763361</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79383227602875162</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.88978336209224385</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97726621242729272</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0583273099476809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1245303078036846</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.1669419657783466</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.2234595968072284</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2673688768185429</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.4052524208130259</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.3420711548776225</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.3746237204310248</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.5617011070794642</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.6327598768442473</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.6615202189009322</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.6516646353793001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.7045159943368395</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.7373318173516272</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2F90-4E0D-B099-9A55D00DDE91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log LE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'50s 5000'!$F$2:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.74742374111624665</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3660422307467972</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8424163357060175</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2323857091921235</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5663329726919635</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.850433268420645</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.1997061448320441</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.3772135738867761</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.5574628841273133</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.7648538651379928</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.9559410389329179</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.0892909981631078</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.2447436488543904</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.3389880912057013</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.459559532335879</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.6057433427060754</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.6882069343890471</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.8284274294341634</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.9430491144744444</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2F90-4E0D-B099-9A55D00DDE91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'10s 1000'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log Ftst</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'5s 500'!$A$2:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'50s 5000'!$G$2:$G$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>-9.1297737411159135E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.20246107062939966</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.4694980145184654</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.39289032070334656</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.4722297124644031</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58251788360406243</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.60705807900684339</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.65152029823422042</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.70307632761567695</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.75620997120951028</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.77863594198596153</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.80567073669837308</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.84296476625340155</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.86902038992565844</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0820777196101774</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.1104213464739563</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.073897894912152</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.1525635142565396</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.1727167434783541</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2F90-4E0D-B099-9A55D00DDE91}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="732662447"/>
+        <c:axId val="732663887"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="732662447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>N, Number</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1" baseline="0"/>
+                  <a:t> of Links</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1200" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732663887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="732663887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" b="1"/>
+                  <a:t>Log Time</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3376,6 +8081,206 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -4886,6 +9791,2521 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5470,26 +12890,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>219074</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>61911</xdr:rowOff>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>71439</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D423A3E3-91D4-28BE-A07A-4A777BC35C6E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E4A97E-06D1-438C-B95D-91CF17A24BAF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5527,6 +12949,216 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2C40498-7A4E-443C-8BC2-2098EF23C70C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>514351</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>128589</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ACE6082-10EB-44F9-A45D-C1BC29AAB9E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>95251</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>147639</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5AD938-F46C-4D31-8AAC-96059532B78F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>228601</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>90489</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4865C85-A5C2-4400-A00A-5BD4B1294E3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>176214</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159200E3-22BF-4A03-9198-F5C712E3D8E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>352426</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>185739</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F257044-8863-4176-8AB7-F33F89695F7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7071,6 +14703,9 @@
       <c r="B15">
         <v>44.761200000000002</v>
       </c>
+      <c r="C15">
+        <v>37393.420100000003</v>
+      </c>
       <c r="D15">
         <v>12.555300000000001</v>
       </c>
@@ -7078,9 +14713,9 @@
         <f t="shared" si="2"/>
         <v>1.6509017209839363</v>
       </c>
-      <c r="F15" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>4.5727951886800122</v>
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
@@ -7094,6 +14729,9 @@
       <c r="B16">
         <v>46.724200000000003</v>
       </c>
+      <c r="C16">
+        <v>46849.981599999999</v>
+      </c>
       <c r="D16">
         <v>15.5246</v>
       </c>
@@ -7101,9 +14739,9 @@
         <f>LOG(B16)</f>
         <v>1.6695418742336443</v>
       </c>
-      <c r="F16" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>4.6707094246577343</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
@@ -7117,6 +14755,9 @@
       <c r="B17">
         <v>50.381500000000003</v>
       </c>
+      <c r="C17">
+        <v>63182.493699999999</v>
+      </c>
       <c r="D17">
         <v>14.525399999999999</v>
       </c>
@@ -7124,9 +14765,9 @@
         <f t="shared" si="2"/>
         <v>1.7022710935317871</v>
       </c>
-      <c r="F17" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>4.8005967627336945</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
@@ -7139,6 +14780,9 @@
       </c>
       <c r="B18">
         <v>53.822499999999998</v>
+      </c>
+      <c r="C18">
+        <v>93029.698300000004</v>
       </c>
       <c r="D18">
         <v>15.210100000000001</v>
@@ -7464,6 +15108,9 @@
       <c r="B11">
         <v>31.0823746999958</v>
       </c>
+      <c r="C11">
+        <v>9546.2483959000092</v>
+      </c>
       <c r="D11">
         <v>9.1464138000155799</v>
       </c>
@@ -7471,9 +15118,9 @@
         <f>LOG(B11)</f>
         <v>1.492514191586626</v>
       </c>
-      <c r="F11" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>3.9798327306341634</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
@@ -7487,6 +15134,9 @@
       <c r="B12">
         <v>37.033908599987598</v>
       </c>
+      <c r="C12">
+        <v>13425.482031699899</v>
+      </c>
       <c r="D12">
         <v>11.198196600016599</v>
       </c>
@@ -7494,9 +15144,9 @@
         <f>LOG(B12)</f>
         <v>1.5685995503920374</v>
       </c>
-      <c r="F12" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>4.1279298876638961</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
@@ -7510,6 +15160,9 @@
       <c r="B13">
         <v>40.702918599999897</v>
       </c>
+      <c r="C13">
+        <v>20349.784599999999</v>
+      </c>
       <c r="D13">
         <v>12.1166240000166</v>
       </c>
@@ -7517,9 +15170,9 @@
         <f t="shared" ref="E13:E19" si="2">LOG(B13)</f>
         <v>1.6096255513979376</v>
       </c>
-      <c r="F13" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>4.30855981663119</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
@@ -7533,6 +15186,9 @@
       <c r="B14">
         <v>44.576451000000802</v>
       </c>
+      <c r="C14">
+        <v>33847.537600000003</v>
+      </c>
       <c r="D14">
         <v>12.8352668000152</v>
       </c>
@@ -7540,9 +15196,9 @@
         <f t="shared" si="2"/>
         <v>1.6491054887186731</v>
       </c>
-      <c r="F14" t="e">
-        <f t="shared" si="0"/>
-        <v>#NUM!</v>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>4.5295270793540778</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
@@ -9618,6 +17274,9 @@
       <c r="B20">
         <v>20.399100000000001</v>
       </c>
+      <c r="C20">
+        <v>36949.504200000003</v>
+      </c>
       <c r="D20">
         <v>6.6779000000000002</v>
       </c>
@@ -9625,9 +17284,9 @@
         <f>LOG(B20)</f>
         <v>1.3096110069525659</v>
       </c>
-      <c r="F20" t="e">
+      <c r="F20">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>4.5676086152707969</v>
       </c>
       <c r="G20">
         <f t="shared" si="4"/>
@@ -9636,6 +17295,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9685,7 +17345,7 @@
         <v>0.25095643933189343</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:G18" si="0">LOG(C2)</f>
+        <f t="shared" ref="F2:G19" si="0">LOG(C2)</f>
         <v>0.51433350099549968</v>
       </c>
       <c r="G2">
@@ -10116,6 +17776,9 @@
       <c r="B19">
         <v>20.060099999999998</v>
       </c>
+      <c r="C19">
+        <v>44037.135799999996</v>
+      </c>
       <c r="D19">
         <v>5.5542999999999996</v>
       </c>
@@ -10123,6 +17786,10 @@
         <f t="shared" si="2"/>
         <v>1.3023330936564801</v>
       </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>4.6438190644616952</v>
+      </c>
       <c r="G19">
         <f t="shared" si="3"/>
         <v>0.74462933325109992</v>
@@ -10135,6 +17802,9 @@
       <c r="B20">
         <v>21.560600000000001</v>
       </c>
+      <c r="C20">
+        <v>55108.906199999998</v>
+      </c>
       <c r="D20">
         <v>5.9722</v>
       </c>
@@ -10142,6 +17812,10 @@
         <f>LOG(B20)</f>
         <v>1.3336608424638372</v>
       </c>
+      <c r="F20">
+        <f t="shared" ref="F20" si="4">LOG(C20)</f>
+        <v>4.7412217912465104</v>
+      </c>
       <c r="G20">
         <f t="shared" si="3"/>
         <v>0.77613434316584407</v>
@@ -10149,6 +17823,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10198,7 +17873,7 @@
         <v>0.37383114507383042</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:G18" si="0">LOG(C2)</f>
+        <f t="shared" ref="F2:G19" si="0">LOG(C2)</f>
         <v>0.71443319838513852</v>
       </c>
       <c r="G2">
@@ -10629,6 +18304,9 @@
       <c r="B19">
         <v>27.515000000000001</v>
       </c>
+      <c r="C19">
+        <v>57286.044000000002</v>
+      </c>
       <c r="D19">
         <v>7.5523999999999996</v>
       </c>
@@ -10636,6 +18314,10 @@
         <f t="shared" si="2"/>
         <v>1.4395695171471754</v>
       </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>4.758048832228817</v>
+      </c>
       <c r="G19">
         <f t="shared" si="3"/>
         <v>0.87808498356654152</v>
@@ -10648,6 +18330,9 @@
       <c r="B20">
         <v>29.072399999999998</v>
       </c>
+      <c r="C20">
+        <v>69179.555800000002</v>
+      </c>
       <c r="D20">
         <v>8.1601999999999997</v>
       </c>
@@ -10655,6 +18340,10 @@
         <f>LOG(B20)</f>
         <v>1.4634808853560093</v>
       </c>
+      <c r="F20">
+        <f t="shared" ref="F20" si="4">LOG(C20)</f>
+        <v>4.8399777690945296</v>
+      </c>
       <c r="G20">
         <f t="shared" si="3"/>
         <v>0.91170080309601198</v>
@@ -10662,6 +18351,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10711,7 +18401,7 @@
         <v>0.46899680905960173</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:G17" si="0">LOG(C2)</f>
+        <f t="shared" ref="F2:G18" si="0">LOG(C2)</f>
         <v>0.74742374111624665</v>
       </c>
       <c r="G2">
@@ -10997,7 +18687,7 @@
         <v>6.3925000000000001</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:E19" si="2">LOG(B13)</f>
+        <f t="shared" ref="E13:F20" si="2">LOG(B13)</f>
         <v>1.3420711548776225</v>
       </c>
       <c r="F13">
@@ -11120,6 +18810,9 @@
       <c r="B18">
         <v>44.8399</v>
       </c>
+      <c r="C18">
+        <v>48776.084499999997</v>
+      </c>
       <c r="D18">
         <v>11.854900000000001</v>
       </c>
@@ -11127,6 +18820,10 @@
         <f t="shared" si="2"/>
         <v>1.6516646353793001</v>
       </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>4.6882069343890471</v>
+      </c>
       <c r="G18">
         <f t="shared" ref="G18:G20" si="3">LOG(D18)</f>
         <v>1.073897894912152</v>
@@ -11139,6 +18836,9 @@
       <c r="B19">
         <v>50.642600000000002</v>
       </c>
+      <c r="C19">
+        <v>67363.932100000005</v>
+      </c>
       <c r="D19">
         <v>14.209</v>
       </c>
@@ -11146,6 +18846,10 @@
         <f t="shared" si="2"/>
         <v>1.7045159943368395</v>
       </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>4.8284274294341634</v>
+      </c>
       <c r="G19">
         <f t="shared" si="3"/>
         <v>1.1525635142565396</v>
@@ -11158,6 +18862,9 @@
       <c r="B20">
         <v>54.6175</v>
       </c>
+      <c r="C20">
+        <v>87710.000700000004</v>
+      </c>
       <c r="D20">
         <v>14.883900000000001</v>
       </c>
@@ -11165,6 +18872,10 @@
         <f>LOG(B20)</f>
         <v>1.7373318173516272</v>
       </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>4.9430491144744444</v>
+      </c>
       <c r="G20">
         <f t="shared" si="3"/>
         <v>1.1727167434783541</v>
@@ -11172,6 +18883,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/ra/time data (version 2).xlsb.xlsx
+++ b/ra/time data (version 2).xlsb.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\uni\masters nu\RA\pythonCode\ra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F5C170-E130-4337-9EBC-B65CD725487F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF410155-A0C0-4D11-A342-5FEAD89CA603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="100s" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="10">
   <si>
     <t>n</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>GA time</t>
+  </si>
+  <si>
+    <t>Log GA</t>
   </si>
 </sst>
 </file>
@@ -1744,7 +1750,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'5s 500'!$E$1</c:f>
+              <c:f>'5s 500'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1831,7 +1837,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'5s 500'!$E$2:$E$20</c:f>
+              <c:f>'5s 500'!$F$2:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -1906,7 +1912,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'5s 500'!$F$1</c:f>
+              <c:f>'5s 500'!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1993,7 +1999,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'5s 500'!$F$2:$F$20</c:f>
+              <c:f>'5s 500'!$G$2:$G$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -2068,7 +2074,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'5s 500'!$G$1</c:f>
+              <c:f>'5s 500'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2155,7 +2161,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'5s 500'!$G$2:$G$20</c:f>
+              <c:f>'5s 500'!$H$2:$H$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -2637,7 +2643,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$E$1</c:f>
+              <c:f>'10s 1000'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2724,7 +2730,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'10s 1000'!$E$2:$E$20</c:f>
+              <c:f>'10s 1000'!$F$2:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -2799,7 +2805,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$F$1</c:f>
+              <c:f>'10s 1000'!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2886,7 +2892,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'10s 1000'!$F$2:$F$20</c:f>
+              <c:f>'10s 1000'!$G$2:$G$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -2961,7 +2967,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$G$1</c:f>
+              <c:f>'10s 1000'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3048,7 +3054,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'10s 1000'!$G$2:$G$20</c:f>
+              <c:f>'10s 1000'!$H$2:$H$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -4430,7 +4436,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$E$1</c:f>
+              <c:f>'10s 1000'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4592,7 +4598,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$F$1</c:f>
+              <c:f>'10s 1000'!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4754,7 +4760,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$G$1</c:f>
+              <c:f>'10s 1000'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5323,7 +5329,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$E$1</c:f>
+              <c:f>'10s 1000'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5485,7 +5491,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$F$1</c:f>
+              <c:f>'10s 1000'!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5647,7 +5653,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$G$1</c:f>
+              <c:f>'10s 1000'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6216,7 +6222,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$E$1</c:f>
+              <c:f>'10s 1000'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6378,7 +6384,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$F$1</c:f>
+              <c:f>'10s 1000'!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6540,7 +6546,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$G$1</c:f>
+              <c:f>'10s 1000'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7109,7 +7115,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$E$1</c:f>
+              <c:f>'10s 1000'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7271,7 +7277,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$F$1</c:f>
+              <c:f>'10s 1000'!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7433,7 +7439,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'10s 1000'!$G$1</c:f>
+              <c:f>'10s 1000'!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12932,16 +12938,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>533401</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>128589</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>590551</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>14289</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15715,7 +15721,7 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15729,16 +15735,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -15752,19 +15764,26 @@
         <v>9.1399999999999995E-2</v>
       </c>
       <c r="E2">
+        <v>0.16077680001035299</v>
+      </c>
+      <c r="F2">
         <f>LOG(B2)</f>
         <v>-0.58854865786206245</v>
       </c>
-      <c r="F2">
-        <f t="shared" ref="F2:G18" si="0">LOG(C2)</f>
+      <c r="G2">
+        <f>LOG(C2)</f>
         <v>-0.26568031914099305</v>
       </c>
-      <c r="G2">
-        <f t="shared" si="0"/>
+      <c r="H2">
+        <f>LOG(D2)</f>
         <v>-1.0390538042661686</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <f>LOG(E2)</f>
+        <v>-0.79377661948310396</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -15778,19 +15797,26 @@
         <v>0.12470000000000001</v>
       </c>
       <c r="E3">
+        <v>0.171153699979186</v>
+      </c>
+      <c r="F3">
         <f>LOG(B3)</f>
         <v>-0.41184038361690795</v>
       </c>
-      <c r="F3">
-        <f t="shared" si="0"/>
+      <c r="G3">
+        <f>LOG(C3)</f>
         <v>0.36310406607463558</v>
       </c>
-      <c r="G3">
-        <f t="shared" si="0"/>
+      <c r="H3">
+        <f>LOG(D3)</f>
         <v>-0.90413354652145739</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <f t="shared" ref="I3:I20" si="0">LOG(E3)</f>
+        <v>-0.76661370790106853</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -15804,19 +15830,26 @@
         <v>0.16689999999999999</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E10" si="1">LOG(B4)</f>
+        <v>0.214481299975886</v>
+      </c>
+      <c r="F4">
+        <f>LOG(B4)</f>
         <v>-0.2438966284148944</v>
       </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
+      <c r="G4">
+        <f>LOG(C4)</f>
         <v>0.89795131674577622</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
+      <c r="H4">
+        <f>LOG(D4)</f>
         <v>-0.77754366332075331</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>-0.66861056674877373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -15830,19 +15863,26 @@
         <v>0.22689999999999999</v>
       </c>
       <c r="E5">
-        <f t="shared" si="1"/>
+        <v>0.261726500000804</v>
+      </c>
+      <c r="F5">
+        <f>LOG(B5)</f>
         <v>-0.18217030025439443</v>
       </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
+      <c r="G5">
+        <f>LOG(C5)</f>
         <v>1.2963492248187813</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
+      <c r="H5">
+        <f>LOG(D5)</f>
         <v>-0.64416550411506401</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>-0.58215230249782446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -15856,19 +15896,26 @@
         <v>0.35560000000000003</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <v>0.31769059994257898</v>
+      </c>
+      <c r="F6">
+        <f>LOG(B6)</f>
         <v>3.4106829707643734E-2</v>
       </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
+      <c r="G6">
+        <f>LOG(C6)</f>
         <v>1.635410352888679</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
+      <c r="H6">
+        <f>LOG(D6)</f>
         <v>-0.44903824770182388</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>-0.49799563519949192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -15882,19 +15929,26 @@
         <v>0.38019999999999998</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <v>0.38544899993576098</v>
+      </c>
+      <c r="F7">
+        <f>LOG(B7)</f>
         <v>6.8482713761754369E-2</v>
       </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
+      <c r="G7">
+        <f>LOG(C7)</f>
         <v>1.9054812401049357</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
+      <c r="H7">
+        <f>LOG(D7)</f>
         <v>-0.41998788747057569</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>-0.4140330767873921</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -15908,19 +15962,26 @@
         <v>0.39839999999999998</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
+        <v>0.42272499995306101</v>
+      </c>
+      <c r="F8">
+        <f>LOG(B8)</f>
         <v>0.13110516209373138</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <f>LOG(C8)</f>
         <v>2.1588402547316026</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
+      <c r="H8">
+        <f>LOG(D8)</f>
         <v>-0.39968067024833892</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>-0.37394206723934081</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -15934,19 +15995,26 @@
         <v>0.44059999999999999</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
+        <v>0.47448320011608303</v>
+      </c>
+      <c r="F9">
+        <f>LOG(B9)</f>
         <v>0.21351775699630487</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
+      <c r="G9">
+        <f>LOG(C9)</f>
         <v>2.3972014278122304</v>
       </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
+      <c r="H9">
+        <f>LOG(D9)</f>
         <v>-0.35595550718525121</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>-0.32377915989853379</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -15960,19 +16028,26 @@
         <v>0.54149999999999998</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
+        <v>0.50923950015567199</v>
+      </c>
+      <c r="F10">
+        <f>LOG(B10)</f>
         <v>0.24968742780530151</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
+      <c r="G10">
+        <f>LOG(C10)</f>
         <v>2.5560865061967952</v>
       </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
+      <c r="H10">
+        <f>LOG(D10)</f>
         <v>-0.26640153903866087</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>-0.29307791681275264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -15986,19 +16061,26 @@
         <v>0.48170000000000002</v>
       </c>
       <c r="E11">
+        <v>0.55982999992556803</v>
+      </c>
+      <c r="F11">
         <f>LOG(B11)</f>
         <v>0.27664559363087632</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
+      <c r="G11">
+        <f>LOG(C11)</f>
         <v>2.7808634738027793</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
+      <c r="H11">
+        <f>LOG(D11)</f>
         <v>-0.31722335368556592</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>-0.25194383246322088</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -16012,19 +16094,26 @@
         <v>0.61350000000000005</v>
       </c>
       <c r="E12">
+        <v>0.61381729994900502</v>
+      </c>
+      <c r="F12">
         <f>LOG(B12)</f>
         <v>0.3280124388555864</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
+      <c r="G12">
+        <f>LOG(C12)</f>
         <v>2.9578717096022213</v>
       </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
+      <c r="H12">
+        <f>LOG(D12)</f>
         <v>-0.21218543293697692</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>-0.21196087548954762</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -16038,19 +16127,26 @@
         <v>0.60750000000000004</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:F20" si="2">LOG(B13)</f>
+        <v>0.67912780004553497</v>
+      </c>
+      <c r="F13">
+        <f>LOG(B13)</f>
         <v>0.3802293369380374</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
+      <c r="G13">
+        <f>LOG(C13)</f>
         <v>3.0642572313915459</v>
       </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
+      <c r="H13">
+        <f>LOG(D13)</f>
         <v>-0.21645371772965016</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>-0.16804849135734951</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -16064,19 +16160,26 @@
         <v>0.63560000000000005</v>
       </c>
       <c r="E14">
-        <f t="shared" si="2"/>
+        <v>0.70740539999678698</v>
+      </c>
+      <c r="F14">
+        <f>LOG(B14)</f>
         <v>0.34161255871200186</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
+      <c r="G14">
+        <f>LOG(C14)</f>
         <v>3.3825190202340627</v>
       </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
+      <c r="H14">
+        <f>LOG(D14)</f>
         <v>-0.19681611146465802</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>-0.15033162931084057</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -16090,19 +16193,26 @@
         <v>1.0444</v>
       </c>
       <c r="E15">
-        <f t="shared" si="2"/>
+        <v>0.75723750004544799</v>
+      </c>
+      <c r="F15">
+        <f>LOG(B15)</f>
         <v>0.40898576821169425</v>
       </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
+      <c r="G15">
+        <f>LOG(C15)</f>
         <v>3.3818388011015577</v>
       </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
+      <c r="H15">
+        <f>LOG(D15)</f>
         <v>1.8866863150906826E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>-0.12076788696980725</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -16116,16 +16226,23 @@
         <v>0.83560000000000001</v>
       </c>
       <c r="E16">
+        <v>0.83966110018081896</v>
+      </c>
+      <c r="F16">
         <f>LOG(B16)</f>
         <v>0.44805671088621207</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
+      <c r="G16">
+        <f>LOG(C16)</f>
         <v>3.5141481507647532</v>
       </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
+      <c r="H16">
+        <f>LOG(D16)</f>
         <v>-7.8001568691729029E-2</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>-7.5895966342748949E-2</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -16142,16 +16259,23 @@
         <v>0.75239999999999996</v>
       </c>
       <c r="E17">
-        <f t="shared" si="2"/>
+        <v>0.85300270002335299</v>
+      </c>
+      <c r="F17">
+        <f>LOG(B17)</f>
         <v>0.41308172370882884</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
+      <c r="G17">
+        <f>LOG(C17)</f>
         <v>3.6022549457863358</v>
       </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
+      <c r="H17">
+        <f>LOG(D17)</f>
         <v>-0.12355121312165876</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>-6.9049594150897398E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -16168,16 +16292,23 @@
         <v>0.80820000000000003</v>
       </c>
       <c r="E18">
-        <f t="shared" si="2"/>
+        <v>0.92503829998895504</v>
+      </c>
+      <c r="F18">
+        <f>LOG(B18)</f>
         <v>0.44745263122699308</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
+      <c r="G18">
+        <f>LOG(C18)</f>
         <v>3.7558622660472802</v>
       </c>
-      <c r="G18">
-        <f t="shared" ref="G18:G20" si="3">LOG(D18)</f>
+      <c r="H18">
+        <f>LOG(D18)</f>
         <v>-9.2481153893370735E-2</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>-3.3840285499332941E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -16194,16 +16325,23 @@
         <v>0.82379999999999998</v>
       </c>
       <c r="E19">
-        <f t="shared" si="2"/>
+        <v>0.95268479990772903</v>
+      </c>
+      <c r="F19">
+        <f>LOG(B19)</f>
         <v>0.48208714182648593</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="2"/>
+      <c r="G19">
+        <f>LOG(C19)</f>
         <v>3.8363828841125054</v>
       </c>
-      <c r="G19">
-        <f t="shared" si="3"/>
+      <c r="H19">
+        <f>LOG(D19)</f>
         <v>-8.4178212379601269E-2</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>-2.1050763898457017E-2</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -16220,16 +16358,23 @@
         <v>0.85919999999999996</v>
       </c>
       <c r="E20">
+        <v>1.0217685999814401</v>
+      </c>
+      <c r="F20">
         <f>LOG(B20)</f>
         <v>0.52937901628761841</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="2"/>
+      <c r="G20">
+        <f>LOG(C20)</f>
         <v>3.8922811035562344</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="3"/>
+      <c r="H20">
+        <f>LOG(D20)</f>
         <v>-6.5905731644519627E-2</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>9.3525522273099487E-3</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -16245,10 +16390,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4F1C10-2E17-488D-A0AD-547086CFA133}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16262,16 +16407,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -16285,19 +16436,26 @@
         <v>0.17069999999999999</v>
       </c>
       <c r="E2">
+        <v>0.24673099978826901</v>
+      </c>
+      <c r="F2">
         <f>LOG(B2)</f>
         <v>-0.28050298338941837</v>
       </c>
-      <c r="F2">
-        <f t="shared" ref="F2:G18" si="0">LOG(C2)</f>
+      <c r="G2">
+        <f>LOG(C2)</f>
         <v>4.9101678208557098E-2</v>
       </c>
-      <c r="G2">
-        <f t="shared" si="0"/>
+      <c r="H2">
+        <f>LOG(D2)</f>
         <v>-0.76776647888526639</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <f>LOG(E2)</f>
+        <v>-0.60777628143370055</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -16311,19 +16469,26 @@
         <v>0.25580000000000003</v>
       </c>
       <c r="E3">
+        <v>0.34577620006166399</v>
+      </c>
+      <c r="F3">
         <f>LOG(B3)</f>
         <v>-0.11599807523121287</v>
       </c>
-      <c r="F3">
-        <f t="shared" si="0"/>
+      <c r="G3">
+        <f>LOG(C3)</f>
         <v>0.67105244589460922</v>
       </c>
-      <c r="G3">
-        <f t="shared" si="0"/>
+      <c r="H3">
+        <f>LOG(D3)</f>
         <v>-0.59209945985736478</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <f t="shared" ref="I3:I20" si="0">LOG(E3)</f>
+        <v>-0.46120490272665071</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -16337,19 +16502,26 @@
         <v>0.34739999999999999</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E10" si="1">LOG(B4)</f>
+        <v>0.45446829986758502</v>
+      </c>
+      <c r="F4">
+        <f>LOG(B4)</f>
         <v>1.7617573339673596E-2</v>
       </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
+      <c r="G4">
+        <f>LOG(C4)</f>
         <v>1.1409100977860087</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
+      <c r="H4">
+        <f>LOG(D4)</f>
         <v>-0.45917018588892017</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>-0.34249640435118378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -16363,19 +16535,26 @@
         <v>0.41699999999999998</v>
       </c>
       <c r="E5">
-        <f t="shared" si="1"/>
+        <v>0.56685939989984002</v>
+      </c>
+      <c r="F5">
+        <f>LOG(B5)</f>
         <v>0.12531857812352648</v>
       </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
+      <c r="G5">
+        <f>LOG(C5)</f>
         <v>1.5271966790930642</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
+      <c r="H5">
+        <f>LOG(D5)</f>
         <v>-0.37986394502624249</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>-0.24652464731471119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -16389,19 +16568,26 @@
         <v>0.50370000000000004</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <v>0.66382870008237604</v>
+      </c>
+      <c r="F6">
+        <f>LOG(B6)</f>
         <v>0.20319612493503247</v>
       </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
+      <c r="G6">
+        <f>LOG(C6)</f>
         <v>1.8585053160566041</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
+      <c r="H6">
+        <f>LOG(D6)</f>
         <v>-0.29782804914228878</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>-0.17794397516037561</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -16415,19 +16601,26 @@
         <v>0.58930000000000005</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
+        <v>0.77235410013236105</v>
+      </c>
+      <c r="F7">
+        <f>LOG(B7)</f>
         <v>0.27535743108759814</v>
       </c>
-      <c r="F7">
-        <f t="shared" si="0"/>
+      <c r="G7">
+        <f>LOG(C7)</f>
         <v>2.1812606136527593</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
+      <c r="H7">
+        <f>LOG(D7)</f>
         <v>-0.22966355890485077</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>-0.11218354360775146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -16441,19 +16634,26 @@
         <v>0.72140000000000004</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
+        <v>0.9346729000099</v>
+      </c>
+      <c r="F8">
+        <f>LOG(B8)</f>
         <v>0.34543254749914665</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <f>LOG(C8)</f>
         <v>2.4659724668498528</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
+      <c r="H8">
+        <f>LOG(D8)</f>
         <v>-0.14182386201765568</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>-2.9340349100993781E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -16467,19 +16667,26 @@
         <v>0.78300000000000003</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
+        <v>1.03519709990359</v>
+      </c>
+      <c r="F9">
+        <f>LOG(B9)</f>
         <v>0.40418349821266247</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
+      <c r="G9">
+        <f>LOG(C9)</f>
         <v>2.6833771387458261</v>
       </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
+      <c r="H9">
+        <f>LOG(D9)</f>
         <v>-0.10623823794205658</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>1.5023046653805916E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -16493,19 +16700,26 @@
         <v>0.85570000000000002</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
+        <v>1.08264300017617</v>
+      </c>
+      <c r="F10">
+        <f>LOG(B10)</f>
         <v>0.44966349415333057</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
+      <c r="G10">
+        <f>LOG(C10)</f>
         <v>2.8452488381001197</v>
       </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
+      <c r="H10">
+        <f>LOG(D10)</f>
         <v>-6.7678468010706816E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>3.4485272310157057E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -16519,19 +16733,26 @@
         <v>0.96150000000000002</v>
       </c>
       <c r="E11">
+        <v>1.25342390011064</v>
+      </c>
+      <c r="F11">
         <f>LOG(B11)</f>
         <v>0.49590494359435922</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
+      <c r="G11">
+        <f>LOG(C11)</f>
         <v>3.10556372742424</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
+      <c r="H11">
+        <f>LOG(D11)</f>
         <v>-1.7050711425501325E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>9.8097971509004067E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -16545,19 +16766,26 @@
         <v>1.0361</v>
       </c>
       <c r="E12">
+        <v>1.3160284000914499</v>
+      </c>
+      <c r="F12">
         <f>LOG(B12)</f>
         <v>0.54841398855423695</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
+      <c r="G12">
+        <f>LOG(C12)</f>
         <v>3.2405537659200929</v>
       </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
+      <c r="H12">
+        <f>LOG(D12)</f>
         <v>1.5401673702949125E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>0.11926526151951455</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -16571,19 +16799,26 @@
         <v>1.1577999999999999</v>
       </c>
       <c r="E13">
-        <f t="shared" ref="E13:F20" si="2">LOG(B13)</f>
+        <v>1.4285178000573</v>
+      </c>
+      <c r="F13">
+        <f>LOG(B13)</f>
         <v>0.582608730687733</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
+      <c r="G13">
+        <f>LOG(C13)</f>
         <v>3.406771963700217</v>
       </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
+      <c r="H13">
+        <f>LOG(D13)</f>
         <v>6.3633545230784669E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>0.15488565628228998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -16597,19 +16832,26 @@
         <v>1.2376</v>
       </c>
       <c r="E14">
-        <f t="shared" si="2"/>
+        <v>1.50050369999371</v>
+      </c>
+      <c r="F14">
+        <f>LOG(B14)</f>
         <v>0.62727366165808607</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
+      <c r="G14">
+        <f>LOG(C14)</f>
         <v>3.5277273291284281</v>
       </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
+      <c r="H14">
+        <f>LOG(D14)</f>
         <v>9.2580300691311124E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>0.17623707066048502</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -16623,19 +16865,26 @@
         <v>1.2986</v>
       </c>
       <c r="E15">
-        <f t="shared" si="2"/>
+        <v>1.6809717998839899</v>
+      </c>
+      <c r="F15">
+        <f>LOG(B15)</f>
         <v>0.6592504687726608</v>
       </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
+      <c r="G15">
+        <f>LOG(C15)</f>
         <v>3.6850515935762131</v>
       </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
+      <c r="H15">
+        <f>LOG(D15)</f>
         <v>0.11347539853673715</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>0.22556042774196874</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -16649,19 +16898,26 @@
         <v>1.4140999999999999</v>
       </c>
       <c r="E16">
+        <v>1.73551960010081</v>
+      </c>
+      <c r="F16">
         <f>LOG(B16)</f>
         <v>0.68306505838291154</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
+      <c r="G16">
+        <f>LOG(C16)</f>
         <v>3.925712216048606</v>
       </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
+      <c r="H16">
+        <f>LOG(D16)</f>
         <v>0.15048012227033458</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>0.23942952274241205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -16675,19 +16931,26 @@
         <v>1.5068999999999999</v>
       </c>
       <c r="E17">
-        <f t="shared" si="2"/>
+        <v>1.8310300000011901</v>
+      </c>
+      <c r="F17">
+        <f>LOG(B17)</f>
         <v>0.72226362737262384</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
+      <c r="G17">
+        <f>LOG(C17)</f>
         <v>4.0496315590090868</v>
       </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
+      <c r="H17">
+        <f>LOG(D17)</f>
         <v>0.17808443287921172</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>0.26269545993699944</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -16701,19 +16964,26 @@
         <v>1.5782</v>
       </c>
       <c r="E18">
-        <f t="shared" si="2"/>
+        <v>1.9423700999468501</v>
+      </c>
+      <c r="F18">
+        <f>LOG(B18)</f>
         <v>0.75321524647887972</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
+      <c r="G18">
+        <f>LOG(C18)</f>
         <v>4.1651177174029792</v>
       </c>
-      <c r="G18">
-        <f t="shared" ref="G18:G20" si="3">LOG(D18)</f>
+      <c r="H18">
+        <f>LOG(D18)</f>
         <v>0.19816203904607557</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>0.28833198409448535</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -16727,19 +16997,26 @@
         <v>1.6807000000000001</v>
       </c>
       <c r="E19">
-        <f t="shared" si="2"/>
+        <v>2.0479162000119602</v>
+      </c>
+      <c r="F19">
+        <f>LOG(B19)</f>
         <v>0.78015162924532189</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="2"/>
+      <c r="G19">
+        <f>LOG(C19)</f>
         <v>4.2150346747474483</v>
       </c>
-      <c r="G19">
-        <f t="shared" si="3"/>
+      <c r="H19">
+        <f>LOG(D19)</f>
         <v>0.22549020007128417</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>0.31131218149471546</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -16753,16 +17030,23 @@
         <v>1.7574000000000001</v>
       </c>
       <c r="E20">
+        <v>2.2034616000019001</v>
+      </c>
+      <c r="F20">
         <f>LOG(B20)</f>
         <v>0.80154090619031826</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="2"/>
+      <c r="G20">
+        <f>LOG(C20)</f>
         <v>4.249645026330171</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="3"/>
+      <c r="H20">
+        <f>LOG(D20)</f>
         <v>0.24487062206524232</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>0.34310548640818223</v>
       </c>
     </row>
   </sheetData>

--- a/ra/time data (version 2).xlsb.xlsx
+++ b/ra/time data (version 2).xlsb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\uni\masters nu\RA\pythonCode\ra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF410155-A0C0-4D11-A342-5FEAD89CA603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9101D87-BA3A-434D-86D6-F4C78D1A24C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2231,6 +2231,102 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5s 500'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Log GA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>'5s 500'!$I$2:$I$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>-0.79377661948310396</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.76661370790106853</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.66861056674877373</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.58215230249782446</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.49799563519949192</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.4140330767873921</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.37394206723934081</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.32377915989853379</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.29307791681275264</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.25194383246322088</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.21196087548954762</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.16804849135734951</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.15033162931084057</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.12076788696980725</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-7.5895966342748949E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-6.9049594150897398E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.3840285499332941E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-2.1050763898457017E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.3525522273099487E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-245C-462D-8B8A-37780AC87CF8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -2481,8 +2577,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.13053999828968746"/>
           <c:y val="0.11762405856546715"/>
-          <c:w val="0.10201027786493486"/>
-          <c:h val="0.1965019209542527"/>
+          <c:w val="6.6754456035186593E-2"/>
+          <c:h val="0.20497131901064805"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -15800,19 +15896,19 @@
         <v>0.171153699979186</v>
       </c>
       <c r="F3">
-        <f>LOG(B3)</f>
+        <f t="shared" ref="F3:F20" si="0">LOG(B3)</f>
         <v>-0.41184038361690795</v>
       </c>
       <c r="G3">
-        <f>LOG(C3)</f>
+        <f t="shared" ref="G3:G20" si="1">LOG(C3)</f>
         <v>0.36310406607463558</v>
       </c>
       <c r="H3">
-        <f>LOG(D3)</f>
+        <f t="shared" ref="H3:H20" si="2">LOG(D3)</f>
         <v>-0.90413354652145739</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I20" si="0">LOG(E3)</f>
+        <f t="shared" ref="I3:I20" si="3">LOG(E3)</f>
         <v>-0.76661370790106853</v>
       </c>
     </row>
@@ -15833,19 +15929,19 @@
         <v>0.214481299975886</v>
       </c>
       <c r="F4">
-        <f>LOG(B4)</f>
+        <f t="shared" si="0"/>
         <v>-0.2438966284148944</v>
       </c>
       <c r="G4">
-        <f>LOG(C4)</f>
+        <f t="shared" si="1"/>
         <v>0.89795131674577622</v>
       </c>
       <c r="H4">
-        <f>LOG(D4)</f>
+        <f t="shared" si="2"/>
         <v>-0.77754366332075331</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.66861056674877373</v>
       </c>
     </row>
@@ -15866,19 +15962,19 @@
         <v>0.261726500000804</v>
       </c>
       <c r="F5">
-        <f>LOG(B5)</f>
+        <f t="shared" si="0"/>
         <v>-0.18217030025439443</v>
       </c>
       <c r="G5">
-        <f>LOG(C5)</f>
+        <f t="shared" si="1"/>
         <v>1.2963492248187813</v>
       </c>
       <c r="H5">
-        <f>LOG(D5)</f>
+        <f t="shared" si="2"/>
         <v>-0.64416550411506401</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.58215230249782446</v>
       </c>
     </row>
@@ -15899,19 +15995,19 @@
         <v>0.31769059994257898</v>
       </c>
       <c r="F6">
-        <f>LOG(B6)</f>
+        <f t="shared" si="0"/>
         <v>3.4106829707643734E-2</v>
       </c>
       <c r="G6">
-        <f>LOG(C6)</f>
+        <f t="shared" si="1"/>
         <v>1.635410352888679</v>
       </c>
       <c r="H6">
-        <f>LOG(D6)</f>
+        <f t="shared" si="2"/>
         <v>-0.44903824770182388</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.49799563519949192</v>
       </c>
     </row>
@@ -15932,19 +16028,19 @@
         <v>0.38544899993576098</v>
       </c>
       <c r="F7">
-        <f>LOG(B7)</f>
+        <f t="shared" si="0"/>
         <v>6.8482713761754369E-2</v>
       </c>
       <c r="G7">
-        <f>LOG(C7)</f>
+        <f t="shared" si="1"/>
         <v>1.9054812401049357</v>
       </c>
       <c r="H7">
-        <f>LOG(D7)</f>
+        <f t="shared" si="2"/>
         <v>-0.41998788747057569</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.4140330767873921</v>
       </c>
     </row>
@@ -15965,19 +16061,19 @@
         <v>0.42272499995306101</v>
       </c>
       <c r="F8">
-        <f>LOG(B8)</f>
+        <f t="shared" si="0"/>
         <v>0.13110516209373138</v>
       </c>
       <c r="G8">
-        <f>LOG(C8)</f>
+        <f t="shared" si="1"/>
         <v>2.1588402547316026</v>
       </c>
       <c r="H8">
-        <f>LOG(D8)</f>
+        <f t="shared" si="2"/>
         <v>-0.39968067024833892</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.37394206723934081</v>
       </c>
     </row>
@@ -15998,19 +16094,19 @@
         <v>0.47448320011608303</v>
       </c>
       <c r="F9">
-        <f>LOG(B9)</f>
+        <f t="shared" si="0"/>
         <v>0.21351775699630487</v>
       </c>
       <c r="G9">
-        <f>LOG(C9)</f>
+        <f t="shared" si="1"/>
         <v>2.3972014278122304</v>
       </c>
       <c r="H9">
-        <f>LOG(D9)</f>
+        <f t="shared" si="2"/>
         <v>-0.35595550718525121</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.32377915989853379</v>
       </c>
     </row>
@@ -16031,19 +16127,19 @@
         <v>0.50923950015567199</v>
       </c>
       <c r="F10">
-        <f>LOG(B10)</f>
+        <f t="shared" si="0"/>
         <v>0.24968742780530151</v>
       </c>
       <c r="G10">
-        <f>LOG(C10)</f>
+        <f t="shared" si="1"/>
         <v>2.5560865061967952</v>
       </c>
       <c r="H10">
-        <f>LOG(D10)</f>
+        <f t="shared" si="2"/>
         <v>-0.26640153903866087</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.29307791681275264</v>
       </c>
     </row>
@@ -16064,19 +16160,19 @@
         <v>0.55982999992556803</v>
       </c>
       <c r="F11">
-        <f>LOG(B11)</f>
+        <f t="shared" si="0"/>
         <v>0.27664559363087632</v>
       </c>
       <c r="G11">
-        <f>LOG(C11)</f>
+        <f t="shared" si="1"/>
         <v>2.7808634738027793</v>
       </c>
       <c r="H11">
-        <f>LOG(D11)</f>
+        <f t="shared" si="2"/>
         <v>-0.31722335368556592</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.25194383246322088</v>
       </c>
     </row>
@@ -16097,19 +16193,19 @@
         <v>0.61381729994900502</v>
       </c>
       <c r="F12">
-        <f>LOG(B12)</f>
+        <f t="shared" si="0"/>
         <v>0.3280124388555864</v>
       </c>
       <c r="G12">
-        <f>LOG(C12)</f>
+        <f t="shared" si="1"/>
         <v>2.9578717096022213</v>
       </c>
       <c r="H12">
-        <f>LOG(D12)</f>
+        <f t="shared" si="2"/>
         <v>-0.21218543293697692</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.21196087548954762</v>
       </c>
     </row>
@@ -16130,19 +16226,19 @@
         <v>0.67912780004553497</v>
       </c>
       <c r="F13">
-        <f>LOG(B13)</f>
+        <f t="shared" si="0"/>
         <v>0.3802293369380374</v>
       </c>
       <c r="G13">
-        <f>LOG(C13)</f>
+        <f t="shared" si="1"/>
         <v>3.0642572313915459</v>
       </c>
       <c r="H13">
-        <f>LOG(D13)</f>
+        <f t="shared" si="2"/>
         <v>-0.21645371772965016</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.16804849135734951</v>
       </c>
     </row>
@@ -16163,19 +16259,19 @@
         <v>0.70740539999678698</v>
       </c>
       <c r="F14">
-        <f>LOG(B14)</f>
+        <f t="shared" si="0"/>
         <v>0.34161255871200186</v>
       </c>
       <c r="G14">
-        <f>LOG(C14)</f>
+        <f t="shared" si="1"/>
         <v>3.3825190202340627</v>
       </c>
       <c r="H14">
-        <f>LOG(D14)</f>
+        <f t="shared" si="2"/>
         <v>-0.19681611146465802</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.15033162931084057</v>
       </c>
     </row>
@@ -16196,19 +16292,19 @@
         <v>0.75723750004544799</v>
       </c>
       <c r="F15">
-        <f>LOG(B15)</f>
+        <f t="shared" si="0"/>
         <v>0.40898576821169425</v>
       </c>
       <c r="G15">
-        <f>LOG(C15)</f>
+        <f t="shared" si="1"/>
         <v>3.3818388011015577</v>
       </c>
       <c r="H15">
-        <f>LOG(D15)</f>
+        <f t="shared" si="2"/>
         <v>1.8866863150906826E-2</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.12076788696980725</v>
       </c>
     </row>
@@ -16229,19 +16325,19 @@
         <v>0.83966110018081896</v>
       </c>
       <c r="F16">
-        <f>LOG(B16)</f>
+        <f t="shared" si="0"/>
         <v>0.44805671088621207</v>
       </c>
       <c r="G16">
-        <f>LOG(C16)</f>
+        <f t="shared" si="1"/>
         <v>3.5141481507647532</v>
       </c>
       <c r="H16">
-        <f>LOG(D16)</f>
+        <f t="shared" si="2"/>
         <v>-7.8001568691729029E-2</v>
       </c>
       <c r="I16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-7.5895966342748949E-2</v>
       </c>
     </row>
@@ -16262,19 +16358,19 @@
         <v>0.85300270002335299</v>
       </c>
       <c r="F17">
-        <f>LOG(B17)</f>
+        <f t="shared" si="0"/>
         <v>0.41308172370882884</v>
       </c>
       <c r="G17">
-        <f>LOG(C17)</f>
+        <f t="shared" si="1"/>
         <v>3.6022549457863358</v>
       </c>
       <c r="H17">
-        <f>LOG(D17)</f>
+        <f t="shared" si="2"/>
         <v>-0.12355121312165876</v>
       </c>
       <c r="I17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-6.9049594150897398E-2</v>
       </c>
     </row>
@@ -16295,19 +16391,19 @@
         <v>0.92503829998895504</v>
       </c>
       <c r="F18">
-        <f>LOG(B18)</f>
+        <f t="shared" si="0"/>
         <v>0.44745263122699308</v>
       </c>
       <c r="G18">
-        <f>LOG(C18)</f>
+        <f t="shared" si="1"/>
         <v>3.7558622660472802</v>
       </c>
       <c r="H18">
-        <f>LOG(D18)</f>
+        <f t="shared" si="2"/>
         <v>-9.2481153893370735E-2</v>
       </c>
       <c r="I18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-3.3840285499332941E-2</v>
       </c>
     </row>
@@ -16328,19 +16424,19 @@
         <v>0.95268479990772903</v>
       </c>
       <c r="F19">
-        <f>LOG(B19)</f>
+        <f t="shared" si="0"/>
         <v>0.48208714182648593</v>
       </c>
       <c r="G19">
-        <f>LOG(C19)</f>
+        <f t="shared" si="1"/>
         <v>3.8363828841125054</v>
       </c>
       <c r="H19">
-        <f>LOG(D19)</f>
+        <f t="shared" si="2"/>
         <v>-8.4178212379601269E-2</v>
       </c>
       <c r="I19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-2.1050763898457017E-2</v>
       </c>
     </row>
@@ -16361,19 +16457,19 @@
         <v>1.0217685999814401</v>
       </c>
       <c r="F20">
-        <f>LOG(B20)</f>
+        <f t="shared" si="0"/>
         <v>0.52937901628761841</v>
       </c>
       <c r="G20">
-        <f>LOG(C20)</f>
+        <f t="shared" si="1"/>
         <v>3.8922811035562344</v>
       </c>
       <c r="H20">
-        <f>LOG(D20)</f>
+        <f t="shared" si="2"/>
         <v>-6.5905731644519627E-2</v>
       </c>
       <c r="I20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9.3525522273099487E-3</v>
       </c>
     </row>
@@ -16472,19 +16568,19 @@
         <v>0.34577620006166399</v>
       </c>
       <c r="F3">
-        <f>LOG(B3)</f>
+        <f t="shared" ref="F3:F20" si="0">LOG(B3)</f>
         <v>-0.11599807523121287</v>
       </c>
       <c r="G3">
-        <f>LOG(C3)</f>
+        <f t="shared" ref="G3:G20" si="1">LOG(C3)</f>
         <v>0.67105244589460922</v>
       </c>
       <c r="H3">
-        <f>LOG(D3)</f>
+        <f t="shared" ref="H3:H20" si="2">LOG(D3)</f>
         <v>-0.59209945985736478</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I20" si="0">LOG(E3)</f>
+        <f t="shared" ref="I3:I20" si="3">LOG(E3)</f>
         <v>-0.46120490272665071</v>
       </c>
     </row>
@@ -16505,19 +16601,19 @@
         <v>0.45446829986758502</v>
       </c>
       <c r="F4">
-        <f>LOG(B4)</f>
+        <f t="shared" si="0"/>
         <v>1.7617573339673596E-2</v>
       </c>
       <c r="G4">
-        <f>LOG(C4)</f>
+        <f t="shared" si="1"/>
         <v>1.1409100977860087</v>
       </c>
       <c r="H4">
-        <f>LOG(D4)</f>
+        <f t="shared" si="2"/>
         <v>-0.45917018588892017</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.34249640435118378</v>
       </c>
     </row>
@@ -16538,19 +16634,19 @@
         <v>0.56685939989984002</v>
       </c>
       <c r="F5">
-        <f>LOG(B5)</f>
+        <f t="shared" si="0"/>
         <v>0.12531857812352648</v>
       </c>
       <c r="G5">
-        <f>LOG(C5)</f>
+        <f t="shared" si="1"/>
         <v>1.5271966790930642</v>
       </c>
       <c r="H5">
-        <f>LOG(D5)</f>
+        <f t="shared" si="2"/>
         <v>-0.37986394502624249</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.24652464731471119</v>
       </c>
     </row>
@@ -16571,19 +16667,19 @@
         <v>0.66382870008237604</v>
       </c>
       <c r="F6">
-        <f>LOG(B6)</f>
+        <f t="shared" si="0"/>
         <v>0.20319612493503247</v>
       </c>
       <c r="G6">
-        <f>LOG(C6)</f>
+        <f t="shared" si="1"/>
         <v>1.8585053160566041</v>
       </c>
       <c r="H6">
-        <f>LOG(D6)</f>
+        <f t="shared" si="2"/>
         <v>-0.29782804914228878</v>
       </c>
       <c r="I6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.17794397516037561</v>
       </c>
     </row>
@@ -16604,19 +16700,19 @@
         <v>0.77235410013236105</v>
       </c>
       <c r="F7">
-        <f>LOG(B7)</f>
+        <f t="shared" si="0"/>
         <v>0.27535743108759814</v>
       </c>
       <c r="G7">
-        <f>LOG(C7)</f>
+        <f t="shared" si="1"/>
         <v>2.1812606136527593</v>
       </c>
       <c r="H7">
-        <f>LOG(D7)</f>
+        <f t="shared" si="2"/>
         <v>-0.22966355890485077</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-0.11218354360775146</v>
       </c>
     </row>
@@ -16637,19 +16733,19 @@
         <v>0.9346729000099</v>
       </c>
       <c r="F8">
-        <f>LOG(B8)</f>
+        <f t="shared" si="0"/>
         <v>0.34543254749914665</v>
       </c>
       <c r="G8">
-        <f>LOG(C8)</f>
+        <f t="shared" si="1"/>
         <v>2.4659724668498528</v>
       </c>
       <c r="H8">
-        <f>LOG(D8)</f>
+        <f t="shared" si="2"/>
         <v>-0.14182386201765568</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-2.9340349100993781E-2</v>
       </c>
     </row>
@@ -16670,19 +16766,19 @@
         <v>1.03519709990359</v>
       </c>
       <c r="F9">
-        <f>LOG(B9)</f>
+        <f t="shared" si="0"/>
         <v>0.40418349821266247</v>
       </c>
       <c r="G9">
-        <f>LOG(C9)</f>
+        <f t="shared" si="1"/>
         <v>2.6833771387458261</v>
       </c>
       <c r="H9">
-        <f>LOG(D9)</f>
+        <f t="shared" si="2"/>
         <v>-0.10623823794205658</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.5023046653805916E-2</v>
       </c>
     </row>
@@ -16703,19 +16799,19 @@
         <v>1.08264300017617</v>
       </c>
       <c r="F10">
-        <f>LOG(B10)</f>
+        <f t="shared" si="0"/>
         <v>0.44966349415333057</v>
       </c>
       <c r="G10">
-        <f>LOG(C10)</f>
+        <f t="shared" si="1"/>
         <v>2.8452488381001197</v>
       </c>
       <c r="H10">
-        <f>LOG(D10)</f>
+        <f t="shared" si="2"/>
         <v>-6.7678468010706816E-2</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3.4485272310157057E-2</v>
       </c>
     </row>
@@ -16736,19 +16832,19 @@
         <v>1.25342390011064</v>
       </c>
       <c r="F11">
-        <f>LOG(B11)</f>
+        <f t="shared" si="0"/>
         <v>0.49590494359435922</v>
       </c>
       <c r="G11">
-        <f>LOG(C11)</f>
+        <f t="shared" si="1"/>
         <v>3.10556372742424</v>
       </c>
       <c r="H11">
-        <f>LOG(D11)</f>
+        <f t="shared" si="2"/>
         <v>-1.7050711425501325E-2</v>
       </c>
       <c r="I11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9.8097971509004067E-2</v>
       </c>
     </row>
@@ -16769,19 +16865,19 @@
         <v>1.3160284000914499</v>
       </c>
       <c r="F12">
-        <f>LOG(B12)</f>
+        <f t="shared" si="0"/>
         <v>0.54841398855423695</v>
       </c>
       <c r="G12">
-        <f>LOG(C12)</f>
+        <f t="shared" si="1"/>
         <v>3.2405537659200929</v>
       </c>
       <c r="H12">
-        <f>LOG(D12)</f>
+        <f t="shared" si="2"/>
         <v>1.5401673702949125E-2</v>
       </c>
       <c r="I12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.11926526151951455</v>
       </c>
     </row>
@@ -16802,19 +16898,19 @@
         <v>1.4285178000573</v>
       </c>
       <c r="F13">
-        <f>LOG(B13)</f>
+        <f t="shared" si="0"/>
         <v>0.582608730687733</v>
       </c>
       <c r="G13">
-        <f>LOG(C13)</f>
+        <f t="shared" si="1"/>
         <v>3.406771963700217</v>
       </c>
       <c r="H13">
-        <f>LOG(D13)</f>
+        <f t="shared" si="2"/>
         <v>6.3633545230784669E-2</v>
       </c>
       <c r="I13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.15488565628228998</v>
       </c>
     </row>
@@ -16835,19 +16931,19 @@
         <v>1.50050369999371</v>
       </c>
       <c r="F14">
-        <f>LOG(B14)</f>
+        <f t="shared" si="0"/>
         <v>0.62727366165808607</v>
       </c>
       <c r="G14">
-        <f>LOG(C14)</f>
+        <f t="shared" si="1"/>
         <v>3.5277273291284281</v>
       </c>
       <c r="H14">
-        <f>LOG(D14)</f>
+        <f t="shared" si="2"/>
         <v>9.2580300691311124E-2</v>
       </c>
       <c r="I14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.17623707066048502</v>
       </c>
     </row>
@@ -16868,19 +16964,19 @@
         <v>1.6809717998839899</v>
       </c>
       <c r="F15">
-        <f>LOG(B15)</f>
+        <f t="shared" si="0"/>
         <v>0.6592504687726608</v>
       </c>
       <c r="G15">
-        <f>LOG(C15)</f>
+        <f t="shared" si="1"/>
         <v>3.6850515935762131</v>
       </c>
       <c r="H15">
-        <f>LOG(D15)</f>
+        <f t="shared" si="2"/>
         <v>0.11347539853673715</v>
       </c>
       <c r="I15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.22556042774196874</v>
       </c>
     </row>
@@ -16901,19 +16997,19 @@
         <v>1.73551960010081</v>
       </c>
       <c r="F16">
-        <f>LOG(B16)</f>
+        <f t="shared" si="0"/>
         <v>0.68306505838291154</v>
       </c>
       <c r="G16">
-        <f>LOG(C16)</f>
+        <f t="shared" si="1"/>
         <v>3.925712216048606</v>
       </c>
       <c r="H16">
-        <f>LOG(D16)</f>
+        <f t="shared" si="2"/>
         <v>0.15048012227033458</v>
       </c>
       <c r="I16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.23942952274241205</v>
       </c>
     </row>
@@ -16934,19 +17030,19 @@
         <v>1.8310300000011901</v>
       </c>
       <c r="F17">
-        <f>LOG(B17)</f>
+        <f t="shared" si="0"/>
         <v>0.72226362737262384</v>
       </c>
       <c r="G17">
-        <f>LOG(C17)</f>
+        <f t="shared" si="1"/>
         <v>4.0496315590090868</v>
       </c>
       <c r="H17">
-        <f>LOG(D17)</f>
+        <f t="shared" si="2"/>
         <v>0.17808443287921172</v>
       </c>
       <c r="I17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.26269545993699944</v>
       </c>
     </row>
@@ -16967,19 +17063,19 @@
         <v>1.9423700999468501</v>
       </c>
       <c r="F18">
-        <f>LOG(B18)</f>
+        <f t="shared" si="0"/>
         <v>0.75321524647887972</v>
       </c>
       <c r="G18">
-        <f>LOG(C18)</f>
+        <f t="shared" si="1"/>
         <v>4.1651177174029792</v>
       </c>
       <c r="H18">
-        <f>LOG(D18)</f>
+        <f t="shared" si="2"/>
         <v>0.19816203904607557</v>
       </c>
       <c r="I18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.28833198409448535</v>
       </c>
     </row>
@@ -17000,19 +17096,19 @@
         <v>2.0479162000119602</v>
       </c>
       <c r="F19">
-        <f>LOG(B19)</f>
+        <f t="shared" si="0"/>
         <v>0.78015162924532189</v>
       </c>
       <c r="G19">
-        <f>LOG(C19)</f>
+        <f t="shared" si="1"/>
         <v>4.2150346747474483</v>
       </c>
       <c r="H19">
-        <f>LOG(D19)</f>
+        <f t="shared" si="2"/>
         <v>0.22549020007128417</v>
       </c>
       <c r="I19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.31131218149471546</v>
       </c>
     </row>
@@ -17033,19 +17129,19 @@
         <v>2.2034616000019001</v>
       </c>
       <c r="F20">
-        <f>LOG(B20)</f>
+        <f t="shared" si="0"/>
         <v>0.80154090619031826</v>
       </c>
       <c r="G20">
-        <f>LOG(C20)</f>
+        <f t="shared" si="1"/>
         <v>4.249645026330171</v>
       </c>
       <c r="H20">
-        <f>LOG(D20)</f>
+        <f t="shared" si="2"/>
         <v>0.24487062206524232</v>
       </c>
       <c r="I20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.34310548640818223</v>
       </c>
     </row>
